--- a/HLJT_online_OpenSesame/hljt_files/Instructions_both_hands.xlsx
+++ b/HLJT_online_OpenSesame/hljt_files/Instructions_both_hands.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github_repos/HLJT/HLJT_local/hljt_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/HLJT/HLJT_local_PsychoPy/hljt_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="13_ncr:1_{CE37664A-FF21-497E-94A9-5762B15D5B2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CD5FD63-E988-4122-BF5C-D27C02CC61FD}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{259D04FF-1AA1-4332-BD96-3244E3FAF37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DE0DBB6-D274-4959-B682-2517E5D6489C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3128DB0A-6163-4D40-98DA-1667AB584357}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -251,23 +249,74 @@
     <t>inst_msg_DE</t>
   </si>
   <si>
-    <t>Anweisungen:
-In dieser Aufgabe sehen Sie Bilder von linken oder rechten Händen, deren Handflächen nach oben oder unten zeigen. Die Bilder werden in verschiedenen Winkeln gedreht.
-Ihre Aufgabe ist es zu bestimmen, ob das Bild einer linken oder rechten Hand entspricht.
-Ihr Ziel ist es, sowohl SCHNELL als auch GENAU zu antworten.
-Jedes Bild wird angezeigt, bis Sie geantwortet haben. Das nächste Bild erscheint automatisch.</t>
-  </si>
-  <si>
     <t>Bitte verwenden Sie nur Ihre Zeigefinger, um zu antworten, und benutzen Sie die Tasten „S“ und „L“ auf Ihrer Tastatur:
 Linke Hand = S | Rechte Hand = L
 Sie müssen Ihre Hände während der gesamten Aufgabe auf der Tastatur halten.
 Halten Sie Ihre Hände in derselben Position und so ruhig wie möglich.</t>
   </si>
   <si>
-    <t>Nach jedem Bild erhalten Sie ein kurzes Feedback zu Ihrer Antwort:
-Wenn Sie korrekt antworten, wird das entsprechende Feld grün.
-Wenn Sie falsch antworten, wird das entsprechende Feld rot.
-Denken Sie daran, dass Ihr Ziel darin besteht, so genau und schnell wie möglich zu antworten.</t>
+    <t>Instruktionen:
+In dieser Aufgabe sehen Sie Bilder von linken oder rechten Händen, deren Handfläche nach oben oder unten zeigt. Die Bilder werden in verschiedenen Winkeln gedreht.
+Ihre Aufgabe ist es zu bestimmen, ob das Bild einer linken oder rechten Hand entspricht.
+Ihr Ziel ist es, so schnell UND korrekt wie möglich zu antworten.
+Jedes Bild wird angezeigt, bis Sie geantwortet haben. Das nächste Bild erscheint automatisch.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nach jedem Bild erhalten Sie ein kurzes Feedback zu Ihrer Antwort:
+Wenn Sie korrekt antworten, wird das entsprechende Feld </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>grün</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+Wenn Sie falsch antworten, wird das entsprechende Feld </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>rot</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Erinnern Sie sich an Ihr Ziel so schnell und korrekt wie möglich zu antworten.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -336,12 +385,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -357,10 +409,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -663,10 +711,10 @@
   <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="36.54296875" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" customWidth="1"/>
-    <col min="4" max="5" width="12.90625" customWidth="1"/>
+    <col min="1" max="1" width="31.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="70.6328125" customWidth="1"/>
+    <col min="6" max="6" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.35">
@@ -692,7 +740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -705,8 +753,8 @@
       <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>19</v>
+      <c r="E2" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="F2">
         <v>0.6</v>
@@ -715,7 +763,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="116" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -729,7 +777,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>0.6</v>
@@ -738,7 +786,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -763,5 +811,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>